--- a/data/trans_orig/P1409-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2012</t>
+          <t>Población con diagnóstico de asma en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430945</t>
+          <t>432068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446507</t>
+          <t>446506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408796</t>
+          <t>408693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423229</t>
+          <t>423447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>846259</t>
+          <t>846103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>866162</t>
+          <t>866729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>664412</t>
+          <t>664235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>679234</t>
+          <t>679135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>577314</t>
+          <t>576940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>596332</t>
+          <t>595820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1248358</t>
+          <t>1247346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1272770</t>
+          <t>1272369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38265</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665920</t>
+          <t>665145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677809</t>
+          <t>677223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681848</t>
+          <t>681550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699469</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1353172</t>
+          <t>1353227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1374785</t>
+          <t>1374173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>15881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598150</t>
+          <t>598736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612454</t>
+          <t>612450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593626</t>
+          <t>593205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609592</t>
+          <t>609625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200823</t>
+          <t>1198552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220121</t>
+          <t>1219078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>22580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28479</t>
+          <t>28697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417588</t>
+          <t>416936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427365</t>
+          <t>427333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424452</t>
+          <t>425220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440517</t>
+          <t>440584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848750</t>
+          <t>848532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>865998</t>
+          <t>866535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30780</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290111</t>
+          <t>290996</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305620</t>
+          <t>305127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337090</t>
+          <t>337477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349210</t>
+          <t>349185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633002</t>
+          <t>633915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651790</t>
+          <t>651922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234763</t>
+          <t>236108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246665</t>
+          <t>246714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367185</t>
+          <t>367439</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382315</t>
+          <t>381379</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608417</t>
+          <t>608416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>625924</t>
+          <t>625946</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50376</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85223</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117167</t>
+          <t>119660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136242</t>
+          <t>139010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189056</t>
+          <t>190369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3341556</t>
+          <t>3341945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3376403</t>
+          <t>3375371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3436749</t>
+          <t>3434256</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3476459</t>
+          <t>3475731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6791638</t>
+          <t>6790325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6844452</t>
+          <t>6841684</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2016</t>
+          <t>Población con diagnóstico de asma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27191</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50534</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393476</t>
+          <t>394329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409314</t>
+          <t>409222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365184</t>
+          <t>364895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381874</t>
+          <t>382291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>764684</t>
+          <t>765330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>788027</t>
+          <t>788436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26931</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565222</t>
+          <t>565676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>580852</t>
+          <t>581601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>531898</t>
+          <t>531677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549144</t>
+          <t>549405</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1103398</t>
+          <t>1103846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1127109</t>
+          <t>1127532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34024</t>
+          <t>33512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49084</t>
+          <t>48419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647144</t>
+          <t>645998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662633</t>
+          <t>662449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627362</t>
+          <t>627874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646676</t>
+          <t>647220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1281399</t>
+          <t>1282064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1306313</t>
+          <t>1305040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>33034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>44048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629916</t>
+          <t>629976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642836</t>
+          <t>642853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615228</t>
+          <t>616043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635577</t>
+          <t>635605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1251316</t>
+          <t>1251077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1275152</t>
+          <t>1275108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456247</t>
+          <t>456450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472010</t>
+          <t>471966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466662</t>
+          <t>465870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485039</t>
+          <t>485188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>927283</t>
+          <t>930726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>952696</t>
+          <t>953586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>30353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322348</t>
+          <t>322565</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332280</t>
+          <t>332329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353336</t>
+          <t>353457</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>369770</t>
+          <t>368646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>681304</t>
+          <t>681739</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>699118</t>
+          <t>699622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233557</t>
+          <t>233636</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247861</t>
+          <t>247724</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367333</t>
+          <t>369014</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>388438</t>
+          <t>389872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608930</t>
+          <t>607164</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>632632</t>
+          <t>633402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>68851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>117063</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165585</t>
+          <t>166235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197780</t>
+          <t>200126</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>257364</t>
+          <t>260204</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3289984</t>
+          <t>3287964</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3325464</t>
+          <t>3325499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3378957</t>
+          <t>3378307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3427479</t>
+          <t>3425304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6681528</t>
+          <t>6678688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6741112</t>
+          <t>6738766</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2023</t>
+          <t>Población con diagnóstico de asma en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56329</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354135</t>
+          <t>353436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390673</t>
+          <t>390652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294325</t>
+          <t>296102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311208</t>
+          <t>310951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>656858</t>
+          <t>657565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697813</t>
+          <t>698483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>43841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>250461</t>
+          <t>260441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302966</t>
+          <t>313305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381805</t>
+          <t>379706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406991</t>
+          <t>405267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261043</t>
+          <t>251063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493763</t>
+          <t>494153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>632085</t>
+          <t>621746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891139</t>
+          <t>889893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>33724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35771</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36129</t>
+          <t>35286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>61418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501172</t>
+          <t>501293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521578</t>
+          <t>521841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506028</t>
+          <t>505852</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>522494</t>
+          <t>522762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1014325</t>
+          <t>1015398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1040687</t>
+          <t>1041530</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33469</t>
+          <t>33679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49550</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76881</t>
+          <t>76174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854317</t>
+          <t>854107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880134</t>
+          <t>879155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662516</t>
+          <t>661223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682845</t>
+          <t>682567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1522971</t>
+          <t>1523678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1565633</t>
+          <t>1564289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31695</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534050</t>
+          <t>534837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550020</t>
+          <t>550241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511600</t>
+          <t>511992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525788</t>
+          <t>525607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1051888</t>
+          <t>1052321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1071705</t>
+          <t>1072844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30688</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41670</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350498</t>
+          <t>350508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360672</t>
+          <t>360805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>576574</t>
+          <t>576196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601715</t>
+          <t>600699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>933039</t>
+          <t>933254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>959531</t>
+          <t>961592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>34166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27868</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268422</t>
+          <t>268187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277507</t>
+          <t>277555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>391315</t>
+          <t>391266</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>404887</t>
+          <t>405176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>663342</t>
+          <t>663533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>680323</t>
+          <t>680144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94673</t>
+          <t>95309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157388</t>
+          <t>159198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153764</t>
+          <t>152418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>476073</t>
+          <t>508248</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273537</t>
+          <t>273464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>630304</t>
+          <t>620534</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3298459</t>
+          <t>3296649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3361174</t>
+          <t>3360538</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3179286</t>
+          <t>3147111</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3501595</t>
+          <t>3502941</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6480903</t>
+          <t>6490673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6837670</t>
+          <t>6837743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P1409-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432068</t>
+          <t>432845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446506</t>
+          <t>446392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408693</t>
+          <t>409866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423447</t>
+          <t>423465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>846103</t>
+          <t>847308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>866729</t>
+          <t>866345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33315</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49996</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>664235</t>
+          <t>663900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>679135</t>
+          <t>679028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>576940</t>
+          <t>577091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>595820</t>
+          <t>596414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1247346</t>
+          <t>1248989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1272369</t>
+          <t>1272155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28024</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>37834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665145</t>
+          <t>665172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677223</t>
+          <t>677652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681550</t>
+          <t>681883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699513</t>
+          <t>699640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1353227</t>
+          <t>1353603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1374173</t>
+          <t>1375086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598736</t>
+          <t>599734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612450</t>
+          <t>612588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593205</t>
+          <t>592850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609625</t>
+          <t>609286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1198552</t>
+          <t>1200848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1219078</t>
+          <t>1219345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28697</t>
+          <t>29610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>416936</t>
+          <t>418798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427333</t>
+          <t>427385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425220</t>
+          <t>424679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440584</t>
+          <t>440655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848532</t>
+          <t>847619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866535</t>
+          <t>865844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290996</t>
+          <t>290167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305127</t>
+          <t>304796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337477</t>
+          <t>337657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349185</t>
+          <t>350060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633915</t>
+          <t>633839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651922</t>
+          <t>652176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236108</t>
+          <t>233935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246714</t>
+          <t>246663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367439</t>
+          <t>367813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>381379</t>
+          <t>382288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608416</t>
+          <t>608543</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>625946</t>
+          <t>625724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84834</t>
+          <t>83690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119660</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139010</t>
+          <t>139304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>190369</t>
+          <t>190443</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3341945</t>
+          <t>3343089</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3375371</t>
+          <t>3376201</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3434256</t>
+          <t>3434626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3475731</t>
+          <t>3475934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6790325</t>
+          <t>6790251</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6841684</t>
+          <t>6841390</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25134</t>
+          <t>25256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>27415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49888</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394329</t>
+          <t>394207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409222</t>
+          <t>410243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>364895</t>
+          <t>365148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>382291</t>
+          <t>381975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765330</t>
+          <t>765254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>788436</t>
+          <t>787803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>24274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>50374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565676</t>
+          <t>566222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>581601</t>
+          <t>581347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>531677</t>
+          <t>531853</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549405</t>
+          <t>550090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1103846</t>
+          <t>1103666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1127532</t>
+          <t>1127365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33512</t>
+          <t>33431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48419</t>
+          <t>49528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645998</t>
+          <t>647449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662449</t>
+          <t>662755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627874</t>
+          <t>627955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647220</t>
+          <t>646398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1282064</t>
+          <t>1280955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1305040</t>
+          <t>1305870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>32706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44048</t>
+          <t>42565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629976</t>
+          <t>629082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642853</t>
+          <t>642174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>616371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635605</t>
+          <t>635451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1251077</t>
+          <t>1252560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1275108</t>
+          <t>1276034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44041</t>
+          <t>45068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456450</t>
+          <t>455905</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471966</t>
+          <t>472383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465870</t>
+          <t>466761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485188</t>
+          <t>485655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>930726</t>
+          <t>929699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>953586</t>
+          <t>953613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>24051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322565</t>
+          <t>322349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332329</t>
+          <t>332324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353457</t>
+          <t>353711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368646</t>
+          <t>368728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>681739</t>
+          <t>680814</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>699622</t>
+          <t>699347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,82 +5784,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>19524</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>11416</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>31511</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>34585</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>23737</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>47244</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>3,61%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>19524</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>10297</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>31155</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>34585</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>23765</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>50003</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233636</t>
+          <t>233296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>247662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,82 +5897,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>380645</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>368658</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>388753</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>622582</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>609923</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>633430</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>96,39%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>380645</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>369014</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>389872</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>622582</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>607164</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>633402</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68851</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106386</t>
+          <t>106829</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>119676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>166235</t>
+          <t>166461</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200126</t>
+          <t>198200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>260204</t>
+          <t>259201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3287964</t>
+          <t>3287521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3325499</t>
+          <t>3325866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3378307</t>
+          <t>3378081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3425304</t>
+          <t>3424866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6678688</t>
+          <t>6679691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6738766</t>
+          <t>6740692</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23886</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>44549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,17 +6755,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>32693</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>53428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -6798,32 +6798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>376686</t>
+          <t>383907</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353436</t>
+          <t>363244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390652</t>
+          <t>397070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306289</t>
+          <t>353705</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296102</t>
+          <t>342273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310951</t>
+          <t>359725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6868,17 +6868,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>682975</t>
+          <t>737612</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>657565</t>
+          <t>716877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>698483</t>
+          <t>752880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,32 +7028,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43841</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87116</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>260441</t>
+          <t>31191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>114897</t>
+          <t>49978</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313305</t>
+          <t>67936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>395765</t>
+          <t>447665</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>379706</t>
+          <t>431423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405267</t>
+          <t>459245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>424388</t>
+          <t>480330</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251063</t>
+          <t>469892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494153</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>820154</t>
+          <t>927995</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621746</t>
+          <t>910037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889893</t>
+          <t>941212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,32 +7371,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33724</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35286</t>
+          <t>39389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61418</t>
+          <t>65396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -7484,32 +7484,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>513466</t>
+          <t>595366</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501293</t>
+          <t>584359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521841</t>
+          <t>604701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>515783</t>
+          <t>593275</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505852</t>
+          <t>583122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>522762</t>
+          <t>601291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1029249</t>
+          <t>1188640</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015398</t>
+          <t>1175530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1041530</t>
+          <t>1201537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076816</t>
+          <t>1240926</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076816</t>
+          <t>1240926</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076816</t>
+          <t>1240926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>52967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>50182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76174</t>
+          <t>76838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>868299</t>
+          <t>679348</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854107</t>
+          <t>668194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879155</t>
+          <t>687447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>673451</t>
+          <t>694423</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>661223</t>
+          <t>683074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682567</t>
+          <t>703612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1541750</t>
+          <t>1373771</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1523678</t>
+          <t>1359820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1564289</t>
+          <t>1386476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>736041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>736041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>736041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599852</t>
+          <t>1436658</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599852</t>
+          <t>1436658</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599852</t>
+          <t>1436658</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>36892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>34094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51079</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>544000</t>
+          <t>591146</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534837</t>
+          <t>580605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550241</t>
+          <t>597468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>518911</t>
+          <t>578110</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511992</t>
+          <t>569184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525607</t>
+          <t>585317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1062911</t>
+          <t>1169256</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1052321</t>
+          <t>1156501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1072844</t>
+          <t>1179351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559304</t>
+          <t>607369</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559304</t>
+          <t>607369</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559304</t>
+          <t>607369</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544096</t>
+          <t>606076</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544096</t>
+          <t>606076</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544096</t>
+          <t>606076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103400</t>
+          <t>1213445</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103400</t>
+          <t>1213445</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103400</t>
+          <t>1213445</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>24931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41455</t>
+          <t>41890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>356381</t>
+          <t>394568</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350508</t>
+          <t>387612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360805</t>
+          <t>399540</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>588586</t>
+          <t>416906</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>576196</t>
+          <t>409103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600699</t>
+          <t>422580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>944967</t>
+          <t>811474</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>933254</t>
+          <t>802341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>961592</t>
+          <t>819300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>438020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974709</t>
+          <t>844231</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974709</t>
+          <t>844231</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974709</t>
+          <t>844231</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26828</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>38788</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>30760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44658</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>273973</t>
+          <t>300635</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268187</t>
+          <t>294038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277555</t>
+          <t>304712</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>398604</t>
+          <t>434982</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>391266</t>
+          <t>425688</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>405176</t>
+          <t>441836</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>672577</t>
+          <t>735619</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>663533</t>
+          <t>725888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>680144</t>
+          <t>743647</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>159198</t>
+          <t>165220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>158583</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>508248</t>
+          <t>200886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>313578</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273464</t>
+          <t>281706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>620534</t>
+          <t>349650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3328571</t>
+          <t>3392637</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3296649</t>
+          <t>3363298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3360538</t>
+          <t>3417107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3426011</t>
+          <t>3551731</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3147111</t>
+          <t>3528541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3502941</t>
+          <t>3570844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6754583</t>
+          <t>6944367</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6490673</t>
+          <t>6908295</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6837743</t>
+          <t>6976239</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
